--- a/sheets/민요/검수/풍년가 (채보2).xlsx
+++ b/sheets/민요/검수/풍년가 (채보2).xlsx
@@ -4,14 +4,14 @@
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="정간목록" sheetId="2" r:id="rId2"/>
-    <sheet name="악보 1" sheetId="3" r:id="rId3"/>
+    <sheet name="악보" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -20,6 +20,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -50,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -73,11 +93,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -96,6 +176,48 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4007,8 +4129,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:Q14"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
@@ -4027,975 +4153,1005 @@
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">풍년가 — 민요채보-2/풍년가.png</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4줄</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3줄</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="N2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="O2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="P2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="Q2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B2">
+        <is>
+          <t xml:space="preserve">풍년가</t>
+        </is>
+      </c>
+      <c s="8" r="C2"/>
+      <c s="8" r="D2"/>
+      <c s="8" r="E2"/>
+      <c s="8" r="F2"/>
+      <c s="8" r="G2"/>
+      <c s="8" r="H2"/>
+      <c s="8" r="I2"/>
+      <c s="8" r="J2"/>
+      <c s="8" r="K2"/>
+      <c s="8" r="L2"/>
+      <c s="8" r="M2"/>
+      <c s="8" r="N2"/>
+      <c s="8" r="O2"/>
+      <c s="8" r="P2"/>
+      <c s="8" r="Q2"/>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">명</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">절</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">얼</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">풍</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="M3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">금</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="O3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">풍</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="P3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="Q3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">풍</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+    <row r="4" ht="56" customHeight="1">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">전</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">년</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="G4" s="17"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">년</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="L4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="M4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">수</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="O4" s="17"/>
+      <c r="P4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="Q4" s="2"/>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="Q4" s="17"/>
+    </row>
+    <row r="5" ht="56" customHeight="1">
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="C5" s="18"/>
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="E5" s="18"/>
+      <c r="F5" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G5" s="18"/>
+      <c r="H5" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="I5" s="18"/>
+      <c r="J5" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="K5" s="18"/>
+      <c r="L5" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="M5" s="18"/>
+      <c r="N5" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="O5" s="18"/>
+      <c r="P5" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="Q5" s="2"/>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="Q5" s="18"/>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">놀</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="E6" s="16"/>
+      <c r="F6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">씨</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">씨</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="L6" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="M6" s="16"/>
+      <c r="N6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">년</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr">
+      <c r="Q6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">년</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
+    <row r="7" ht="56" customHeight="1">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="E7" s="17"/>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 南</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="G7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="H7" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 南</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="I7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="J7" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="K7" s="3"/>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="K7" s="19"/>
+      <c r="L7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="M7" s="17"/>
+      <c r="N7" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 南</t>
-        </is>
-      </c>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+          </r>
+        </is>
+      </c>
+      <c r="O7" s="17"/>
+      <c r="P7" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 南</t>
-        </is>
-      </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="Q7" s="17"/>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">를</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">⁚
 ‹</t>
         </is>
       </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="E8" s="18"/>
+      <c r="F8" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I8" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J8" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="K8" s="18"/>
+      <c r="L8" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 △
 ‹</t>
-        </is>
-      </c>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="M8" s="18"/>
+      <c r="N8" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O8" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P8" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q8" s="2" t="inlineStr">
+      <c r="Q8" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
+    <row r="9" ht="56" customHeight="1">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">춘</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">좋</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">좋</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">왔</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="L9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="M9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">강</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">왔</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q9" s="2" t="inlineStr">
+      <c r="Q9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">왔</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
+    <row r="10" ht="56" customHeight="1">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C10" s="17"/>
+      <c r="D10" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">삼</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="F10" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 姑</t>
-        </is>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="G10" s="17"/>
+      <c r="H10" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="I10" s="17"/>
+      <c r="J10" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="K10" s="17"/>
+      <c r="L10" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="M10" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">산</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="N10" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 姑</t>
-        </is>
-      </c>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="O10" s="17"/>
+      <c r="P10" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="Q10" s="2"/>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="Q10" s="17"/>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C11" s="18"/>
+      <c r="D11" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="E11" s="18"/>
+      <c r="F11" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 仲</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="I11" s="18"/>
+      <c r="J11" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="K11" s="18"/>
+      <c r="L11" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="M11" s="18"/>
+      <c r="N11" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 仲</t>
         </is>
       </c>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="O11" s="18"/>
+      <c r="P11" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="Q11" s="2"/>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="Q11" s="18"/>
+    </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">세</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">월</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">좋</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="L12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="M12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">으</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="O12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="P12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="Q12" s="2" t="inlineStr">
+      <c r="Q12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2" t="inlineStr">
+    <row r="13" ht="56" customHeight="1">
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="C13" s="17"/>
+      <c r="D13" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="G13" s="17"/>
+      <c r="H13" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I13" s="17"/>
+      <c r="J13" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="K13" s="17"/>
+      <c r="L13" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="M13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">로</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="N13" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2" t="inlineStr">
+      <c r="O13" s="17"/>
+      <c r="P13" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="Q13" s="2"/>
-    </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="Q13" s="17"/>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 △</t>
-        </is>
-      </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="C14" s="18"/>
+      <c r="D14" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="E14" s="18"/>
+      <c r="F14" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">黃
 僙</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H14" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="I14" s="18"/>
+      <c r="J14" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 ○</t>
-        </is>
-      </c>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="K14" s="18"/>
+      <c r="L14" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="M14" s="2"/>
-      <c r="N14" s="3" t="inlineStr">
+      <c r="M14" s="18"/>
+      <c r="N14" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">黃
 僙</t>
         </is>
       </c>
-      <c r="O14" s="3"/>
-      <c r="P14" s="2" t="inlineStr">
+      <c r="O14" s="20"/>
+      <c r="P14" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="Q14" s="2"/>
+      <c r="Q14" s="18"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:Q2"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" scale="76"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/풍년가 (채보2).xlsx
+++ b/sheets/민요/검수/풍년가 (채보2).xlsx
@@ -413,7 +413,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -701,12 +701,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|南</t>
+          <t xml:space="preserve">–|南</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 南</t>
         </is>
       </c>
@@ -1143,12 +1143,12 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|南</t>
+          <t xml:space="preserve">–|南</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 南</t>
         </is>
       </c>
@@ -1257,12 +1257,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|姑</t>
+          <t xml:space="preserve">–|姑</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 姑</t>
         </is>
       </c>
@@ -1557,12 +1557,12 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I29" s="2"/>
@@ -1627,12 +1627,12 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△|‹</t>
+          <t xml:space="preserve">–|△|‹</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △
 ‹</t>
         </is>
@@ -2272,12 +2272,12 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I48" s="2"/>
@@ -2307,12 +2307,12 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|○</t>
+          <t xml:space="preserve">–|○</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 ○</t>
         </is>
       </c>
@@ -2491,12 +2491,12 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|南</t>
+          <t xml:space="preserve">–|南</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 南</t>
         </is>
       </c>
@@ -2719,12 +2719,12 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I60" s="2"/>
@@ -2937,12 +2937,12 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|南</t>
+          <t xml:space="preserve">–|南</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 南</t>
         </is>
       </c>
@@ -3055,12 +3055,12 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|姑</t>
+          <t xml:space="preserve">–|姑</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 姑</t>
         </is>
       </c>
@@ -3777,12 +3777,12 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I88" s="2"/>
@@ -4085,12 +4085,12 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I96" s="2"/>
@@ -4120,12 +4120,12 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -4340,7 +4340,7 @@
       <c r="A5" s="0"/>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C5" s="10"/>
@@ -4439,7 +4439,7 @@
       </c>
       <c r="L6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M6" s="8"/>
@@ -4484,7 +4484,7 @@
       <c r="E7" s="9"/>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 南</t>
         </is>
       </c>
@@ -4495,7 +4495,7 @@
       </c>
       <c r="H7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 南</t>
         </is>
       </c>
@@ -4518,14 +4518,14 @@
       <c r="M7" s="9"/>
       <c r="N7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 南</t>
         </is>
       </c>
       <c r="O7" s="9"/>
       <c r="P7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 南</t>
         </is>
       </c>
@@ -4580,7 +4580,7 @@
       <c r="K8" s="10"/>
       <c r="L8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △
 ‹</t>
         </is>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="F10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 姑</t>
         </is>
       </c>
@@ -4744,7 +4744,7 @@
       </c>
       <c r="N10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 姑</t>
         </is>
       </c>
@@ -4905,7 +4905,7 @@
       <c r="A13" s="0"/>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C13" s="9"/>
@@ -4929,13 +4929,13 @@
       <c r="G13" s="9"/>
       <c r="H13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I13" s="9"/>
       <c r="J13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K13" s="9"/>
@@ -4968,7 +4968,7 @@
       <c r="A14" s="0"/>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -4999,7 +4999,7 @@
       <c r="I14" s="10"/>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 ○</t>
         </is>
       </c>

--- a/sheets/민요/검수/풍년가 (채보2).xlsx
+++ b/sheets/민요/검수/풍년가 (채보2).xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,30 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4165,105 +4203,105 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">풍년가</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
       </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">명</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">절</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="H3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">얼</t>
         </is>
       </c>
-      <c r="J3" s="17" t="inlineStr">
+      <c r="J3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="K3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">풍</t>
         </is>
       </c>
-      <c r="L3" s="17" t="inlineStr">
+      <c r="L3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr">
+      <c r="M3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">금</t>
         </is>
       </c>
-      <c r="N3" s="17" t="inlineStr">
+      <c r="N3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O3" s="8" t="inlineStr">
+      <c r="O3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">풍</t>
         </is>
       </c>
-      <c r="P3" s="17" t="inlineStr">
+      <c r="P3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q3" s="8" t="inlineStr">
+      <c r="Q3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">풍</t>
         </is>
@@ -4271,194 +4309,194 @@
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">전</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">년</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G4" s="9"/>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="G4" s="23"/>
+      <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I4" s="9"/>
-      <c r="J4" s="17" t="inlineStr">
+      <c r="I4" s="23"/>
+      <c r="J4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="K4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">년</t>
         </is>
       </c>
-      <c r="L4" s="17" t="inlineStr">
+      <c r="L4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M4" s="9" t="inlineStr">
+      <c r="M4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">수</t>
         </is>
       </c>
-      <c r="N4" s="17" t="inlineStr">
+      <c r="N4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="O4" s="9"/>
-      <c r="P4" s="17" t="inlineStr">
+      <c r="O4" s="23"/>
+      <c r="P4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="Q4" s="9"/>
+      <c r="Q4" s="23"/>
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="C5" s="24"/>
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E5" s="10"/>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="E5" s="24"/>
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G5" s="10"/>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="G5" s="24"/>
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I5" s="10"/>
-      <c r="J5" s="17" t="inlineStr">
+      <c r="I5" s="24"/>
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K5" s="10"/>
-      <c r="L5" s="17" t="inlineStr">
+      <c r="K5" s="24"/>
+      <c r="L5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M5" s="10"/>
-      <c r="N5" s="17" t="inlineStr">
+      <c r="M5" s="24"/>
+      <c r="N5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="O5" s="10"/>
-      <c r="P5" s="17" t="inlineStr">
+      <c r="O5" s="24"/>
+      <c r="P5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="Q5" s="10"/>
+      <c r="Q5" s="24"/>
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">놀</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E6" s="8"/>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="E6" s="22"/>
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="G6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">씨</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">씨</t>
         </is>
       </c>
-      <c r="J6" s="17" t="inlineStr">
+      <c r="J6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="K6" s="8" t="inlineStr">
+      <c r="K6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="L6" s="17" t="inlineStr">
+      <c r="L6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M6" s="8"/>
-      <c r="N6" s="17" t="inlineStr">
+      <c r="M6" s="22"/>
+      <c r="N6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="O6" s="8" t="inlineStr">
+      <c r="O6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">년</t>
         </is>
       </c>
-      <c r="P6" s="17" t="inlineStr">
+      <c r="P6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="Q6" s="8" t="inlineStr">
+      <c r="Q6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">년</t>
         </is>
@@ -4466,142 +4504,142 @@
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="E7" s="23"/>
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 南</t>
         </is>
       </c>
-      <c r="G7" s="9" t="inlineStr">
+      <c r="G7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 南</t>
         </is>
       </c>
-      <c r="I7" s="9" t="inlineStr">
+      <c r="I7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
       </c>
-      <c r="J7" s="18" t="inlineStr">
+      <c r="J7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="K7" s="12"/>
-      <c r="L7" s="17" t="inlineStr">
+      <c r="K7" s="26"/>
+      <c r="L7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M7" s="9"/>
-      <c r="N7" s="17" t="inlineStr">
+      <c r="M7" s="23"/>
+      <c r="N7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 南</t>
         </is>
       </c>
-      <c r="O7" s="9"/>
-      <c r="P7" s="17" t="inlineStr">
+      <c r="O7" s="23"/>
+      <c r="P7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 南</t>
         </is>
       </c>
-      <c r="Q7" s="9"/>
+      <c r="Q7" s="23"/>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">를</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">⁚
 ‹</t>
         </is>
       </c>
-      <c r="E8" s="10"/>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="E8" s="24"/>
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="G8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I8" s="10" t="inlineStr">
+      <c r="I8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="J8" s="17" t="inlineStr">
+      <c r="J8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="K8" s="10"/>
-      <c r="L8" s="17" t="inlineStr">
+      <c r="K8" s="24"/>
+      <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △
 ‹</t>
         </is>
       </c>
-      <c r="M8" s="10"/>
-      <c r="N8" s="17" t="inlineStr">
+      <c r="M8" s="24"/>
+      <c r="N8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O8" s="10" t="inlineStr">
+      <c r="O8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="P8" s="17" t="inlineStr">
+      <c r="P8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q8" s="10" t="inlineStr">
+      <c r="Q8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -4609,82 +4647,82 @@
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">춘</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">좋</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I9" s="8" t="inlineStr">
+      <c r="I9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">좋</t>
         </is>
       </c>
-      <c r="J9" s="17" t="inlineStr">
+      <c r="J9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K9" s="8" t="inlineStr">
+      <c r="K9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">왔</t>
         </is>
       </c>
-      <c r="L9" s="17" t="inlineStr">
+      <c r="L9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M9" s="8" t="inlineStr">
+      <c r="M9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">강</t>
         </is>
       </c>
-      <c r="N9" s="17" t="inlineStr">
+      <c r="N9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="O9" s="8" t="inlineStr">
+      <c r="O9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">왔</t>
         </is>
       </c>
-      <c r="P9" s="17" t="inlineStr">
+      <c r="P9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q9" s="8" t="inlineStr">
+      <c r="Q9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">왔</t>
         </is>
@@ -4692,210 +4730,210 @@
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="C10" s="23"/>
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">삼</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 姑</t>
         </is>
       </c>
-      <c r="G10" s="9"/>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="G10" s="23"/>
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="I10" s="9"/>
-      <c r="J10" s="17" t="inlineStr">
+      <c r="I10" s="23"/>
+      <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="K10" s="9"/>
-      <c r="L10" s="17" t="inlineStr">
+      <c r="K10" s="23"/>
+      <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="M10" s="9" t="inlineStr">
+      <c r="M10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">산</t>
         </is>
       </c>
-      <c r="N10" s="17" t="inlineStr">
+      <c r="N10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 姑</t>
         </is>
       </c>
-      <c r="O10" s="9"/>
-      <c r="P10" s="17" t="inlineStr">
+      <c r="O10" s="23"/>
+      <c r="P10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="Q10" s="9"/>
+      <c r="Q10" s="23"/>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="C11" s="24"/>
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="E11" s="10"/>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="E11" s="24"/>
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 仲</t>
         </is>
       </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="G11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
       </c>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I11" s="10"/>
-      <c r="J11" s="17" t="inlineStr">
+      <c r="I11" s="24"/>
+      <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="K11" s="10"/>
-      <c r="L11" s="17" t="inlineStr">
+      <c r="K11" s="24"/>
+      <c r="L11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="M11" s="10"/>
-      <c r="N11" s="17" t="inlineStr">
+      <c r="M11" s="24"/>
+      <c r="N11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 仲</t>
         </is>
       </c>
-      <c r="O11" s="10"/>
-      <c r="P11" s="17" t="inlineStr">
+      <c r="O11" s="24"/>
+      <c r="P11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="Q11" s="10"/>
+      <c r="Q11" s="24"/>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">세</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">월</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="G12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">좋</t>
         </is>
       </c>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I12" s="8" t="inlineStr">
+      <c r="I12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="J12" s="17" t="inlineStr">
+      <c r="J12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K12" s="8" t="inlineStr">
+      <c r="K12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
       </c>
-      <c r="L12" s="17" t="inlineStr">
+      <c r="L12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M12" s="8" t="inlineStr">
+      <c r="M12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">으</t>
         </is>
       </c>
-      <c r="N12" s="17" t="inlineStr">
+      <c r="N12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O12" s="8" t="inlineStr">
+      <c r="O12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
       </c>
-      <c r="P12" s="17" t="inlineStr">
+      <c r="P12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="Q12" s="8" t="inlineStr">
+      <c r="Q12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
@@ -4903,127 +4941,127 @@
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="C13" s="23"/>
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="G13" s="9"/>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="G13" s="23"/>
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I13" s="9"/>
-      <c r="J13" s="17" t="inlineStr">
+      <c r="I13" s="23"/>
+      <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K13" s="9"/>
-      <c r="L13" s="17" t="inlineStr">
+      <c r="K13" s="23"/>
+      <c r="L13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="M13" s="9" t="inlineStr">
+      <c r="M13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">로</t>
         </is>
       </c>
-      <c r="N13" s="17" t="inlineStr">
+      <c r="N13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="O13" s="9"/>
-      <c r="P13" s="17" t="inlineStr">
+      <c r="O13" s="23"/>
+      <c r="P13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="Q13" s="9"/>
+      <c r="Q13" s="23"/>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="C14" s="24"/>
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="E14" s="10"/>
-      <c r="F14" s="18" t="inlineStr">
+      <c r="E14" s="24"/>
+      <c r="F14" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">黃
 僙</t>
         </is>
       </c>
-      <c r="G14" s="13" t="inlineStr">
+      <c r="G14" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I14" s="10"/>
-      <c r="J14" s="17" t="inlineStr">
+      <c r="I14" s="24"/>
+      <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 ○</t>
         </is>
       </c>
-      <c r="K14" s="10"/>
-      <c r="L14" s="17" t="inlineStr">
+      <c r="K14" s="24"/>
+      <c r="L14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="M14" s="10"/>
-      <c r="N14" s="18" t="inlineStr">
+      <c r="M14" s="24"/>
+      <c r="N14" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">黃
 僙</t>
         </is>
       </c>
-      <c r="O14" s="13"/>
-      <c r="P14" s="17" t="inlineStr">
+      <c r="O14" s="27"/>
+      <c r="P14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="Q14" s="10"/>
+      <c r="Q14" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/풍년가 (채보2).xlsx
+++ b/sheets/민요/검수/풍년가 (채보2).xlsx
@@ -4180,28 +4180,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="12" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="82.06" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4224,7 +4224,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="82.06" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="82.06" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4331,13 +4331,13 @@
       </c>
       <c r="F4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G4" s="23"/>
       <c r="H4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I4" s="23"/>
@@ -4363,18 +4363,18 @@
       </c>
       <c r="N4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O4" s="23"/>
       <c r="P4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q4" s="23"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="82.06" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4384,13 +4384,13 @@
       <c r="C5" s="24"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E5" s="24"/>
       <c r="F5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G5" s="24"/>
@@ -4402,19 +4402,19 @@
       <c r="I5" s="24"/>
       <c r="J5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K5" s="24"/>
       <c r="L5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M5" s="24"/>
       <c r="N5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O5" s="24"/>
@@ -4425,7 +4425,7 @@
       </c>
       <c r="Q5" s="24"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="82.06" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="D6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E6" s="22"/>
@@ -4502,7 +4502,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="82.06" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="25" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
       </c>
       <c r="D7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E7" s="23"/>
@@ -4550,7 +4550,7 @@
       <c r="K7" s="26"/>
       <c r="L7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M7" s="23"/>
@@ -4569,7 +4569,7 @@
       </c>
       <c r="Q7" s="23"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="82.06" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="82.06" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="82.06" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
       </c>
       <c r="Q10" s="23"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="82.06" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
       </c>
       <c r="Q11" s="24"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="82.06" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="82.06" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -4997,12 +4997,12 @@
       <c r="O13" s="23"/>
       <c r="P13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="82.06" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="H14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I14" s="24"/>
@@ -5058,7 +5058,7 @@
       <c r="O14" s="27"/>
       <c r="P14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q14" s="24"/>

--- a/sheets/민요/검수/풍년가 (채보2).xlsx
+++ b/sheets/민요/검수/풍년가 (채보2).xlsx
@@ -1665,14 +1665,13 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|△|‹</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-△
-‹</t>
+△</t>
         </is>
       </c>
       <c r="I31" s="2"/>
@@ -3471,13 +3470,12 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚|‹</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚
-‹</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I79" s="2"/>
@@ -4201,7 +4199,7 @@
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="82.06" customHeight="1">
+    <row r="2" ht="55.19" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4224,7 +4222,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="82.06" customHeight="1">
+    <row r="3" ht="55.19" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4307,7 +4305,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="82.06" customHeight="1">
+    <row r="4" ht="55.19" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4374,7 +4372,7 @@
       </c>
       <c r="Q4" s="23"/>
     </row>
-    <row r="5" ht="82.06" customHeight="1">
+    <row r="5" ht="55.19" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4425,7 +4423,7 @@
       </c>
       <c r="Q5" s="24"/>
     </row>
-    <row r="6" ht="82.06" customHeight="1">
+    <row r="6" ht="55.19" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4502,7 +4500,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="82.06" customHeight="1">
+    <row r="7" ht="55.19" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="25" t="inlineStr">
         <is>
@@ -4569,7 +4567,7 @@
       </c>
       <c r="Q7" s="23"/>
     </row>
-    <row r="8" ht="82.06" customHeight="1">
+    <row r="8" ht="55.19" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4584,8 +4582,7 @@
       </c>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚
-‹</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E8" s="24"/>
@@ -4619,8 +4616,7 @@
       <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-△
-‹</t>
+△</t>
         </is>
       </c>
       <c r="M8" s="24"/>
@@ -4645,7 +4641,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="82.06" customHeight="1">
+    <row r="9" ht="55.19" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4728,7 +4724,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="82.06" customHeight="1">
+    <row r="10" ht="55.19" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4795,7 +4791,7 @@
       </c>
       <c r="Q10" s="23"/>
     </row>
-    <row r="11" ht="82.06" customHeight="1">
+    <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4856,7 +4852,7 @@
       </c>
       <c r="Q11" s="24"/>
     </row>
-    <row r="12" ht="82.06" customHeight="1">
+    <row r="12" ht="55.19" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -4939,7 +4935,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="82.06" customHeight="1">
+    <row r="13" ht="55.19" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -5002,7 +4998,7 @@
       </c>
       <c r="Q13" s="23"/>
     </row>
-    <row r="14" ht="82.06" customHeight="1">
+    <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>

--- a/sheets/민요/검수/풍년가 (채보2).xlsx
+++ b/sheets/민요/검수/풍년가 (채보2).xlsx
@@ -2344,13 +2344,12 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|○</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-○</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I49" s="2"/>
@@ -5033,8 +5032,7 @@
       <c r="I14" s="24"/>
       <c r="J14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-○</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K14" s="24"/>

--- a/sheets/민요/검수/풍년가 (채보2).xlsx
+++ b/sheets/민요/검수/풍년가 (채보2).xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -233,6 +238,21 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4228,7 +4248,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="C3" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
@@ -4238,7 +4258,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E3" s="22" t="inlineStr">
+      <c r="E3" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">명</t>
         </is>
@@ -4248,7 +4268,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G3" s="22" t="inlineStr">
+      <c r="G3" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">절</t>
         </is>
@@ -4258,7 +4278,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I3" s="22" t="inlineStr">
+      <c r="I3" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">얼</t>
         </is>
@@ -4268,7 +4288,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K3" s="22" t="inlineStr">
+      <c r="K3" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">풍</t>
         </is>
@@ -4278,7 +4298,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M3" s="22" t="inlineStr">
+      <c r="M3" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">금</t>
         </is>
@@ -4288,7 +4308,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O3" s="22" t="inlineStr">
+      <c r="O3" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">풍</t>
         </is>
@@ -4298,7 +4318,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q3" s="22" t="inlineStr">
+      <c r="Q3" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">풍</t>
         </is>
@@ -4311,7 +4331,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C4" s="23" t="inlineStr">
+      <c r="C4" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">전</t>
         </is>
@@ -4321,7 +4341,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E4" s="23" t="inlineStr">
+      <c r="E4" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">년</t>
         </is>
@@ -4331,19 +4351,19 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G4" s="23"/>
+      <c r="G4" s="29"/>
       <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I4" s="23"/>
+      <c r="I4" s="29"/>
       <c r="J4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K4" s="23" t="inlineStr">
+      <c r="K4" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">년</t>
         </is>
@@ -4353,7 +4373,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M4" s="23" t="inlineStr">
+      <c r="M4" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">수</t>
         </is>
@@ -4363,13 +4383,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O4" s="23"/>
+      <c r="O4" s="29"/>
       <c r="P4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q4" s="23"/>
+      <c r="Q4" s="29"/>
     </row>
     <row r="5" ht="55.19" customHeight="1">
       <c r="A5" s="0"/>
@@ -4378,49 +4398,49 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C5" s="24"/>
+      <c r="C5" s="30"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E5" s="24"/>
+      <c r="E5" s="30"/>
       <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G5" s="24"/>
+      <c r="G5" s="30"/>
       <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I5" s="24"/>
+      <c r="I5" s="30"/>
       <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K5" s="24"/>
+      <c r="K5" s="30"/>
       <c r="L5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M5" s="24"/>
+      <c r="M5" s="30"/>
       <c r="N5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O5" s="24"/>
+      <c r="O5" s="30"/>
       <c r="P5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="Q5" s="24"/>
+      <c r="Q5" s="30"/>
     </row>
     <row r="6" ht="55.19" customHeight="1">
       <c r="A6" s="0"/>
@@ -4430,7 +4450,7 @@
 潢</t>
         </is>
       </c>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="C6" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">놀</t>
         </is>
@@ -4440,13 +4460,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E6" s="22"/>
+      <c r="E6" s="28"/>
       <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G6" s="22" t="inlineStr">
+      <c r="G6" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">씨</t>
         </is>
@@ -4456,7 +4476,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I6" s="22" t="inlineStr">
+      <c r="I6" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">씨</t>
         </is>
@@ -4467,7 +4487,7 @@
 潢</t>
         </is>
       </c>
-      <c r="K6" s="22" t="inlineStr">
+      <c r="K6" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -4477,13 +4497,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M6" s="22"/>
+      <c r="M6" s="28"/>
       <c r="N6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="O6" s="22" t="inlineStr">
+      <c r="O6" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">년</t>
         </is>
@@ -4493,7 +4513,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="Q6" s="22" t="inlineStr">
+      <c r="Q6" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">년</t>
         </is>
@@ -4506,7 +4526,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="C7" s="26" t="inlineStr">
+      <c r="C7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -4516,14 +4536,14 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E7" s="23"/>
+      <c r="E7" s="29"/>
       <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 南</t>
         </is>
       </c>
-      <c r="G7" s="23" t="inlineStr">
+      <c r="G7" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
@@ -4534,7 +4554,7 @@
 南</t>
         </is>
       </c>
-      <c r="I7" s="23" t="inlineStr">
+      <c r="I7" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
@@ -4544,27 +4564,27 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="K7" s="26"/>
+      <c r="K7" s="31"/>
       <c r="L7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M7" s="23"/>
+      <c r="M7" s="29"/>
       <c r="N7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 南</t>
         </is>
       </c>
-      <c r="O7" s="23"/>
+      <c r="O7" s="29"/>
       <c r="P7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 南</t>
         </is>
       </c>
-      <c r="Q7" s="23"/>
+      <c r="Q7" s="29"/>
     </row>
     <row r="8" ht="55.19" customHeight="1">
       <c r="A8" s="0"/>
@@ -4574,7 +4594,7 @@
 無</t>
         </is>
       </c>
-      <c r="C8" s="24" t="inlineStr">
+      <c r="C8" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">를</t>
         </is>
@@ -4584,13 +4604,13 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="E8" s="24"/>
+      <c r="E8" s="30"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G8" s="24" t="inlineStr">
+      <c r="G8" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -4600,7 +4620,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I8" s="24" t="inlineStr">
+      <c r="I8" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -4611,20 +4631,20 @@
 無</t>
         </is>
       </c>
-      <c r="K8" s="24"/>
+      <c r="K8" s="30"/>
       <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="M8" s="24"/>
+      <c r="M8" s="30"/>
       <c r="N8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O8" s="24" t="inlineStr">
+      <c r="O8" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -4634,7 +4654,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q8" s="24" t="inlineStr">
+      <c r="Q8" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -4647,7 +4667,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
@@ -4657,7 +4677,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="E9" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">춘</t>
         </is>
@@ -4667,7 +4687,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G9" s="22" t="inlineStr">
+      <c r="G9" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">좋</t>
         </is>
@@ -4677,7 +4697,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I9" s="22" t="inlineStr">
+      <c r="I9" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">좋</t>
         </is>
@@ -4687,7 +4707,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K9" s="22" t="inlineStr">
+      <c r="K9" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">왔</t>
         </is>
@@ -4697,7 +4717,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M9" s="22" t="inlineStr">
+      <c r="M9" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">강</t>
         </is>
@@ -4707,7 +4727,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="O9" s="22" t="inlineStr">
+      <c r="O9" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">왔</t>
         </is>
@@ -4717,7 +4737,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q9" s="22" t="inlineStr">
+      <c r="Q9" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">왔</t>
         </is>
@@ -4731,14 +4751,14 @@
 南</t>
         </is>
       </c>
-      <c r="C10" s="23"/>
+      <c r="C10" s="29"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="E10" s="23" t="inlineStr">
+      <c r="E10" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">삼</t>
         </is>
@@ -4749,28 +4769,28 @@
 姑</t>
         </is>
       </c>
-      <c r="G10" s="23"/>
+      <c r="G10" s="29"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="I10" s="23"/>
+      <c r="I10" s="29"/>
       <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="K10" s="23"/>
+      <c r="K10" s="29"/>
       <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="M10" s="23" t="inlineStr">
+      <c r="M10" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">산</t>
         </is>
@@ -4781,14 +4801,14 @@
 姑</t>
         </is>
       </c>
-      <c r="O10" s="23"/>
+      <c r="O10" s="29"/>
       <c r="P10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="Q10" s="23"/>
+      <c r="Q10" s="29"/>
     </row>
     <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
@@ -4798,21 +4818,21 @@
 姑</t>
         </is>
       </c>
-      <c r="C11" s="24"/>
+      <c r="C11" s="30"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="E11" s="24"/>
+      <c r="E11" s="30"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 仲</t>
         </is>
       </c>
-      <c r="G11" s="24" t="inlineStr">
+      <c r="G11" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
@@ -4822,34 +4842,34 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I11" s="24"/>
+      <c r="I11" s="30"/>
       <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="K11" s="24"/>
+      <c r="K11" s="30"/>
       <c r="L11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="M11" s="24"/>
+      <c r="M11" s="30"/>
       <c r="N11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 仲</t>
         </is>
       </c>
-      <c r="O11" s="24"/>
+      <c r="O11" s="30"/>
       <c r="P11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="Q11" s="24"/>
+      <c r="Q11" s="30"/>
     </row>
     <row r="12" ht="55.19" customHeight="1">
       <c r="A12" s="0"/>
@@ -4858,7 +4878,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C12" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">세</t>
         </is>
@@ -4868,7 +4888,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="E12" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">월</t>
         </is>
@@ -4878,7 +4898,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G12" s="22" t="inlineStr">
+      <c r="G12" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">좋</t>
         </is>
@@ -4888,7 +4908,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I12" s="22" t="inlineStr">
+      <c r="I12" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -4898,7 +4918,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K12" s="22" t="inlineStr">
+      <c r="K12" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
@@ -4908,7 +4928,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M12" s="22" t="inlineStr">
+      <c r="M12" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">으</t>
         </is>
@@ -4918,7 +4938,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O12" s="22" t="inlineStr">
+      <c r="O12" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
@@ -4928,7 +4948,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="Q12" s="22" t="inlineStr">
+      <c r="Q12" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
@@ -4941,14 +4961,14 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C13" s="23"/>
+      <c r="C13" s="29"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="E13" s="23" t="inlineStr">
+      <c r="E13" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -4959,26 +4979,26 @@
 姑</t>
         </is>
       </c>
-      <c r="G13" s="23"/>
+      <c r="G13" s="29"/>
       <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I13" s="23"/>
+      <c r="I13" s="29"/>
       <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K13" s="23"/>
+      <c r="K13" s="29"/>
       <c r="L13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="M13" s="23" t="inlineStr">
+      <c r="M13" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">로</t>
         </is>
@@ -4989,13 +5009,13 @@
 姑</t>
         </is>
       </c>
-      <c r="O13" s="23"/>
+      <c r="O13" s="29"/>
       <c r="P13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q13" s="23"/>
+      <c r="Q13" s="29"/>
     </row>
     <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
@@ -5005,21 +5025,21 @@
 △</t>
         </is>
       </c>
-      <c r="C14" s="24"/>
+      <c r="C14" s="30"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="E14" s="24"/>
+      <c r="E14" s="30"/>
       <c r="F14" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">黃
 僙</t>
         </is>
       </c>
-      <c r="G14" s="27" t="inlineStr">
+      <c r="G14" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -5029,33 +5049,33 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I14" s="24"/>
+      <c r="I14" s="30"/>
       <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K14" s="24"/>
+      <c r="K14" s="30"/>
       <c r="L14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="M14" s="24"/>
+      <c r="M14" s="30"/>
       <c r="N14" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">黃
 僙</t>
         </is>
       </c>
-      <c r="O14" s="27"/>
+      <c r="O14" s="32"/>
       <c r="P14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q14" s="24"/>
+      <c r="Q14" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/풍년가 (채보2).xlsx
+++ b/sheets/민요/검수/풍년가 (채보2).xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -42,11 +42,6 @@
     </font>
     <font>
       <sz val="24"/>
-      <name val="궁서체"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -155,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -232,25 +227,10 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -363,7 +343,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
     </row>
@@ -423,7 +403,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">제목 오른쪽에 "C#key". 인쇄된 양식(12정간, 굵은 선 3칸마다). 8줄 사용. 민요채보-1/풍년가와 같은 곡의 다른 채보본. 8줄 12정간에 체크(✓)·점 등 꾸밈 일부 포함. AI 재판독 초안.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 제목 '풍년가 (굿거리)', 오른쪽 위 C#key. 인쇄 양식 12정간·굵은 선 3칸마다 → 3/4·12. 오른쪽부터 8줄 사용(왼쪽 2줄 빈 줄 제외). 줄1~4 1절(풍년이 왔네…금수강산으로), 줄5~8 2절(얼씨구나 좋다…화전놀이를 가세)로 같은 가락 반복. 연음 짧은 가로/사선 획은 –, 아주 작은 점은 ·. 줄4 정간11 체크(✓)는 ^ 로 적음. 한 곡.</t>
         </is>
       </c>
     </row>
@@ -983,12 +963,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I12" s="2"/>
@@ -1018,12 +998,13 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–
+△</t>
         </is>
       </c>
       <c r="I13" s="2"/>
@@ -1395,11 +1376,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">네</t>
-        </is>
-      </c>
+      <c r="I23" s="2"/>
       <c r="J23" s="4"/>
       <c r="K23" s="2"/>
     </row>
@@ -1462,19 +1439,23 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">黃|僙</t>
+          <t xml:space="preserve">黃|㒇</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">黃
-僙</t>
-        </is>
-      </c>
-      <c r="I25" s="3"/>
+㒇</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">네</t>
+        </is>
+      </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙 확실치 않음</t>
+          <t xml:space="preserve">위 글자 黃(위에 작은 획, 潢?), 아래 亻無</t>
         </is>
       </c>
       <c r="K25" s="2"/>
@@ -1580,12 +1561,12 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I28" s="2"/>
@@ -1648,18 +1629,22 @@
       <c r="F30" s="2">
         <v>2</v>
       </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I30" s="2"/>
-      <c r="J30" s="4"/>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I30" s="3"/>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">작은 사선 획(–/·?)</t>
+        </is>
+      </c>
       <c r="K30" s="2"/>
     </row>
     <row r="31">
@@ -1683,19 +1668,22 @@
       <c r="F31" s="2">
         <v>2</v>
       </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–|△</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-△</t>
-        </is>
-      </c>
-      <c r="I31" s="2"/>
-      <c r="J31" s="4"/>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I31" s="3"/>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">작은 사선 획(–/·?)</t>
+        </is>
+      </c>
       <c r="K31" s="2"/>
     </row>
     <row r="32">
@@ -2029,12 +2017,12 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I40" s="2"/>
@@ -2102,22 +2090,18 @@
       <c r="F42" s="2">
         <v>2</v>
       </c>
-      <c r="G42" s="3" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="H42" s="3" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="I42" s="3"/>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㴌 확실치 않음</t>
-        </is>
-      </c>
+      <c r="I42" s="2"/>
+      <c r="J42" s="4"/>
       <c r="K42" s="2"/>
     </row>
     <row r="43">
@@ -2327,18 +2311,22 @@
       <c r="F48" s="2">
         <v>4</v>
       </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I48" s="2"/>
-      <c r="J48" s="4"/>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">^</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">^</t>
+        </is>
+      </c>
+      <c r="I48" s="3"/>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">체크(✓) 모양</t>
+        </is>
+      </c>
       <c r="K48" s="2"/>
     </row>
     <row r="49">
@@ -2364,12 +2352,12 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="I49" s="2"/>
@@ -2438,12 +2426,12 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I51" s="2"/>
@@ -2773,18 +2761,22 @@
       <c r="F60" s="2">
         <v>4</v>
       </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I60" s="2"/>
-      <c r="J60" s="4"/>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I60" s="3"/>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">작은 점 두 개 세로(⁚/·?)</t>
+        </is>
+      </c>
       <c r="K60" s="2"/>
     </row>
     <row r="61">
@@ -2810,12 +2802,13 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–
+△</t>
         </is>
       </c>
       <c r="I61" s="2"/>
@@ -3158,7 +3151,7 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구</t>
+          <t xml:space="preserve">구나</t>
         </is>
       </c>
       <c r="J70" s="4"/>
@@ -3262,13 +3255,13 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">黃|僙</t>
+          <t xml:space="preserve">黃|㒇</t>
         </is>
       </c>
       <c r="H73" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">黃
-僙</t>
+㒇</t>
         </is>
       </c>
       <c r="I73" s="3" t="inlineStr">
@@ -3278,7 +3271,7 @@
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙 확실치 않음</t>
+          <t xml:space="preserve">아래 亻無</t>
         </is>
       </c>
       <c r="K73" s="2"/>
@@ -3382,18 +3375,22 @@
       <c r="F76" s="2">
         <v>1</v>
       </c>
-      <c r="G76" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I76" s="2"/>
-      <c r="J76" s="4"/>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I76" s="3"/>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">작은 사선 획(–/·?)</t>
+        </is>
+      </c>
       <c r="K76" s="2"/>
     </row>
     <row r="77">
@@ -3419,12 +3416,12 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I77" s="2"/>
@@ -3454,12 +3451,12 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I78" s="2"/>
@@ -3489,12 +3486,12 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I79" s="2"/>
@@ -3905,26 +3902,22 @@
       <c r="F90" s="2">
         <v>2</v>
       </c>
-      <c r="G90" s="3" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="H90" s="3" t="inlineStr">
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="I90" s="3" t="inlineStr">
+      <c r="I90" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="J90" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㴌 확실치 않음</t>
-        </is>
-      </c>
+      <c r="J90" s="4"/>
       <c r="K90" s="2"/>
     </row>
     <row r="91">
@@ -4140,12 +4133,12 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="I96" s="2"/>
@@ -4175,13 +4168,12 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|△</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-△</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I97" s="2"/>
@@ -4218,7 +4210,7 @@
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="55.19" customHeight="1">
+    <row r="2" ht="52.21" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4241,14 +4233,14 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="55.19" customHeight="1">
+    <row r="3" ht="52.21" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C3" s="28" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
@@ -4258,7 +4250,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E3" s="28" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">명</t>
         </is>
@@ -4268,7 +4260,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G3" s="28" t="inlineStr">
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">절</t>
         </is>
@@ -4278,7 +4270,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I3" s="28" t="inlineStr">
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">얼</t>
         </is>
@@ -4288,7 +4280,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K3" s="28" t="inlineStr">
+      <c r="K3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">풍</t>
         </is>
@@ -4298,7 +4290,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M3" s="28" t="inlineStr">
+      <c r="M3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">금</t>
         </is>
@@ -4308,7 +4300,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O3" s="28" t="inlineStr">
+      <c r="O3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">풍</t>
         </is>
@@ -4318,20 +4310,20 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q3" s="28" t="inlineStr">
+      <c r="Q3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">풍</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="55.19" customHeight="1">
+    <row r="4" ht="52.21" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C4" s="29" t="inlineStr">
+      <c r="C4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">전</t>
         </is>
@@ -4341,7 +4333,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E4" s="29" t="inlineStr">
+      <c r="E4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">년</t>
         </is>
@@ -4351,19 +4343,19 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G4" s="29"/>
+      <c r="G4" s="23"/>
       <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I4" s="29"/>
+      <c r="I4" s="23"/>
       <c r="J4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K4" s="29" t="inlineStr">
+      <c r="K4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">년</t>
         </is>
@@ -4373,7 +4365,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M4" s="29" t="inlineStr">
+      <c r="M4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">수</t>
         </is>
@@ -4383,66 +4375,66 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O4" s="29"/>
+      <c r="O4" s="23"/>
       <c r="P4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q4" s="29"/>
-    </row>
-    <row r="5" ht="55.19" customHeight="1">
+      <c r="Q4" s="23"/>
+    </row>
+    <row r="5" ht="52.21" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C5" s="30"/>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="C5" s="24"/>
+      <c r="D5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E5" s="30"/>
+      <c r="E5" s="26"/>
       <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G5" s="30"/>
+      <c r="G5" s="24"/>
       <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I5" s="30"/>
+      <c r="I5" s="24"/>
       <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K5" s="30"/>
+      <c r="K5" s="24"/>
       <c r="L5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M5" s="30"/>
+      <c r="M5" s="24"/>
       <c r="N5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O5" s="30"/>
+      <c r="O5" s="24"/>
       <c r="P5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="Q5" s="30"/>
-    </row>
-    <row r="6" ht="55.19" customHeight="1">
+      <c r="Q5" s="24"/>
+    </row>
+    <row r="6" ht="52.21" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4450,7 +4442,7 @@
 潢</t>
         </is>
       </c>
-      <c r="C6" s="28" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">놀</t>
         </is>
@@ -4460,13 +4452,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E6" s="28"/>
+      <c r="E6" s="22"/>
       <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G6" s="28" t="inlineStr">
+      <c r="G6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">씨</t>
         </is>
@@ -4476,7 +4468,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I6" s="28" t="inlineStr">
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">씨</t>
         </is>
@@ -4487,7 +4479,7 @@
 潢</t>
         </is>
       </c>
-      <c r="K6" s="28" t="inlineStr">
+      <c r="K6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -4497,13 +4489,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M6" s="28"/>
+      <c r="M6" s="22"/>
       <c r="N6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="O6" s="28" t="inlineStr">
+      <c r="O6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">년</t>
         </is>
@@ -4513,20 +4505,20 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="Q6" s="28" t="inlineStr">
+      <c r="Q6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">년</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="55.19" customHeight="1">
+    <row r="7" ht="52.21" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="C7" s="31" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -4536,14 +4528,14 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E7" s="29"/>
+      <c r="E7" s="23"/>
       <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 南</t>
         </is>
       </c>
-      <c r="G7" s="29" t="inlineStr">
+      <c r="G7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
@@ -4554,39 +4546,39 @@
 南</t>
         </is>
       </c>
-      <c r="I7" s="29" t="inlineStr">
+      <c r="I7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
       </c>
-      <c r="J7" s="25" t="inlineStr">
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="K7" s="31"/>
-      <c r="L7" s="21" t="inlineStr">
+      <c r="K7" s="23"/>
+      <c r="L7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M7" s="29"/>
+      <c r="M7" s="27"/>
       <c r="N7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 南</t>
         </is>
       </c>
-      <c r="O7" s="29"/>
+      <c r="O7" s="23"/>
       <c r="P7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 南</t>
         </is>
       </c>
-      <c r="Q7" s="29"/>
-    </row>
-    <row r="8" ht="55.19" customHeight="1">
+      <c r="Q7" s="23"/>
+    </row>
+    <row r="8" ht="52.21" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4594,23 +4586,23 @@
 無</t>
         </is>
       </c>
-      <c r="C8" s="30" t="inlineStr">
+      <c r="C8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">를</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E8" s="30"/>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="E8" s="24"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G8" s="30" t="inlineStr">
+      <c r="G8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -4620,7 +4612,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I8" s="30" t="inlineStr">
+      <c r="I8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -4631,451 +4623,452 @@
 無</t>
         </is>
       </c>
-      <c r="K8" s="30"/>
-      <c r="L8" s="21" t="inlineStr">
+      <c r="K8" s="24"/>
+      <c r="L8" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="M8" s="26"/>
+      <c r="N8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="O8" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이</t>
+        </is>
+      </c>
+      <c r="P8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="Q8" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="52.21" customHeight="1">
+      <c r="A9" s="0"/>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">춘</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">좋</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">좋</t>
+        </is>
+      </c>
+      <c r="J9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="K9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">왔</t>
+        </is>
+      </c>
+      <c r="L9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="M9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">강</t>
+        </is>
+      </c>
+      <c r="N9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="O9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">왔</t>
+        </is>
+      </c>
+      <c r="P9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">왔</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="52.21" customHeight="1">
+      <c r="A10" s="0"/>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="C10" s="23"/>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">삼</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+姑</t>
+        </is>
+      </c>
+      <c r="G10" s="23"/>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲
+姑</t>
+        </is>
+      </c>
+      <c r="I10" s="23"/>
+      <c r="J10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="K10" s="23"/>
+      <c r="L10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="M10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">산</t>
+        </is>
+      </c>
+      <c r="N10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+姑</t>
+        </is>
+      </c>
+      <c r="O10" s="23"/>
+      <c r="P10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲
+姑</t>
+        </is>
+      </c>
+      <c r="Q10" s="23"/>
+    </row>
+    <row r="11" ht="52.21" customHeight="1">
+      <c r="A11" s="0"/>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲
+姑</t>
+        </is>
+      </c>
+      <c r="C11" s="24"/>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+無</t>
+        </is>
+      </c>
+      <c r="E11" s="24"/>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+仲</t>
+        </is>
+      </c>
+      <c r="G11" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">구
+나</t>
+        </is>
+      </c>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I11" s="24"/>
+      <c r="J11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲
+姑</t>
+        </is>
+      </c>
+      <c r="K11" s="24"/>
+      <c r="L11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+無</t>
+        </is>
+      </c>
+      <c r="M11" s="24"/>
+      <c r="N11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+仲</t>
+        </is>
+      </c>
+      <c r="O11" s="24"/>
+      <c r="P11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="Q11" s="24"/>
+    </row>
+    <row r="12" ht="52.21" customHeight="1">
+      <c r="A12" s="0"/>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">세</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">월</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">좋</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="I12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다</t>
+        </is>
+      </c>
+      <c r="J12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="K12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">네</t>
+        </is>
+      </c>
+      <c r="L12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="M12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">으</t>
+        </is>
+      </c>
+      <c r="N12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O12" s="22"/>
+      <c r="P12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="Q12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">네</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="52.21" customHeight="1">
+      <c r="A13" s="0"/>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="C13" s="23"/>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲
+姑</t>
+        </is>
+      </c>
+      <c r="G13" s="23"/>
+      <c r="H13" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I13" s="27"/>
+      <c r="J13" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">^</t>
+        </is>
+      </c>
+      <c r="K13" s="27"/>
+      <c r="L13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="M13" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">로</t>
+        </is>
+      </c>
+      <c r="N13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲
+姑</t>
+        </is>
+      </c>
+      <c r="O13" s="23"/>
+      <c r="P13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="Q13" s="23"/>
+    </row>
+    <row r="14" ht="52.21" customHeight="1">
+      <c r="A14" s="0"/>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="C14" s="24"/>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲
+姑</t>
+        </is>
+      </c>
+      <c r="E14" s="24"/>
+      <c r="F14" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">黃
+㒇</t>
+        </is>
+      </c>
+      <c r="G14" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아</t>
+        </is>
+      </c>
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="M8" s="30"/>
-      <c r="N8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="O8" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이</t>
-        </is>
-      </c>
-      <c r="P8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="Q8" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="55.19" customHeight="1">
-      <c r="A9" s="0"/>
-      <c r="B9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="C9" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가</t>
-        </is>
-      </c>
-      <c r="D9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="E9" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">춘</t>
-        </is>
-      </c>
-      <c r="F9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G9" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">좋</t>
-        </is>
-      </c>
-      <c r="H9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I9" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">좋</t>
-        </is>
-      </c>
-      <c r="J9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="K9" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">왔</t>
-        </is>
-      </c>
-      <c r="L9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="M9" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">강</t>
-        </is>
-      </c>
-      <c r="N9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="O9" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">왔</t>
-        </is>
-      </c>
-      <c r="P9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="Q9" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">왔</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="55.19" customHeight="1">
-      <c r="A10" s="0"/>
-      <c r="B10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無
-南</t>
-        </is>
-      </c>
-      <c r="C10" s="29"/>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無
-南</t>
-        </is>
-      </c>
-      <c r="E10" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">삼</t>
-        </is>
-      </c>
-      <c r="F10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-姑</t>
-        </is>
-      </c>
-      <c r="G10" s="29"/>
-      <c r="H10" s="21" t="inlineStr">
+      <c r="I14" s="24"/>
+      <c r="J14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="K14" s="24"/>
+      <c r="L14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="I10" s="29"/>
-      <c r="J10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無
-南</t>
-        </is>
-      </c>
-      <c r="K10" s="29"/>
-      <c r="L10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無
-南</t>
-        </is>
-      </c>
-      <c r="M10" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">산</t>
-        </is>
-      </c>
-      <c r="N10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-姑</t>
-        </is>
-      </c>
-      <c r="O10" s="29"/>
-      <c r="P10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲
-姑</t>
-        </is>
-      </c>
-      <c r="Q10" s="29"/>
-    </row>
-    <row r="11" ht="55.19" customHeight="1">
-      <c r="A11" s="0"/>
-      <c r="B11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲
-姑</t>
-        </is>
-      </c>
-      <c r="C11" s="30"/>
-      <c r="D11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-無</t>
-        </is>
-      </c>
-      <c r="E11" s="30"/>
-      <c r="F11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南
-仲</t>
-        </is>
-      </c>
-      <c r="G11" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">구</t>
-        </is>
-      </c>
-      <c r="H11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I11" s="30"/>
-      <c r="J11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲
-姑</t>
-        </is>
-      </c>
-      <c r="K11" s="30"/>
-      <c r="L11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-無</t>
-        </is>
-      </c>
-      <c r="M11" s="30"/>
-      <c r="N11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南
-仲</t>
-        </is>
-      </c>
-      <c r="O11" s="30"/>
-      <c r="P11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="Q11" s="30"/>
-    </row>
-    <row r="12" ht="55.19" customHeight="1">
-      <c r="A12" s="0"/>
-      <c r="B12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="C12" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">세</t>
-        </is>
-      </c>
-      <c r="D12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="E12" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">월</t>
-        </is>
-      </c>
-      <c r="F12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G12" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">좋</t>
-        </is>
-      </c>
-      <c r="H12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="I12" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">다</t>
-        </is>
-      </c>
-      <c r="J12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="K12" s="28" t="inlineStr">
+      <c r="M14" s="24"/>
+      <c r="N14" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">黃
+㒇</t>
+        </is>
+      </c>
+      <c r="O14" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
       </c>
-      <c r="L12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="M12" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">으</t>
-        </is>
-      </c>
-      <c r="N12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O12" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">네</t>
-        </is>
-      </c>
-      <c r="P12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="Q12" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">네</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="55.19" customHeight="1">
-      <c r="A13" s="0"/>
-      <c r="B13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="C13" s="29"/>
-      <c r="D13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無
-南</t>
-        </is>
-      </c>
-      <c r="E13" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">에</t>
-        </is>
-      </c>
-      <c r="F13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲
-姑</t>
-        </is>
-      </c>
-      <c r="G13" s="29"/>
-      <c r="H13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I13" s="29"/>
-      <c r="J13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="K13" s="29"/>
-      <c r="L13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無
-南</t>
-        </is>
-      </c>
-      <c r="M13" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">로</t>
-        </is>
-      </c>
-      <c r="N13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲
-姑</t>
-        </is>
-      </c>
-      <c r="O13" s="29"/>
-      <c r="P13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="Q13" s="29"/>
-    </row>
-    <row r="14" ht="55.19" customHeight="1">
-      <c r="A14" s="0"/>
-      <c r="B14" s="21" t="inlineStr">
+      <c r="P14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="C14" s="30"/>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲
-姑</t>
-        </is>
-      </c>
-      <c r="E14" s="30"/>
-      <c r="F14" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">黃
-僙</t>
-        </is>
-      </c>
-      <c r="G14" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아</t>
-        </is>
-      </c>
-      <c r="H14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I14" s="30"/>
-      <c r="J14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="K14" s="30"/>
-      <c r="L14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲
-姑</t>
-        </is>
-      </c>
-      <c r="M14" s="30"/>
-      <c r="N14" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">黃
-僙</t>
-        </is>
-      </c>
-      <c r="O14" s="32"/>
-      <c r="P14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="Q14" s="30"/>
+      <c r="Q14" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="1">
